--- a/public/download/ozon-tul-vual-molochnaya-annotacii.xlsx
+++ b/public/download/ozon-tul-vual-molochnaya-annotacii.xlsx
@@ -512,7 +512,7 @@
 Ширина 200 см, высота 220 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -559,7 +559,7 @@
 Ширина 200 см, высота 225 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -606,7 +606,7 @@
 Ширина 200 см, высота 230 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -653,7 +653,7 @@
 Ширина 200 см, высота 235 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -700,7 +700,7 @@
 Ширина 200 см, высота 240 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -747,7 +747,7 @@
 Ширина 200 см, высота 245 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -794,7 +794,7 @@
 Ширина 200 см, высота 250 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -841,7 +841,7 @@
 Ширина 200 см, высота 255 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -888,7 +888,7 @@
 Ширина 200 см, высота 260 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -935,7 +935,7 @@
 Ширина 200 см, высота 265 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -982,7 +982,7 @@
 Ширина 200 см, высота 270 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1029,7 +1029,7 @@
 Ширина 200 см, высота 275 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1076,7 +1076,7 @@
 Ширина 200 см, высота 280 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1123,7 +1123,7 @@
 Ширина 200 см, высота 285 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1170,7 +1170,7 @@
 Ширина 200 см, высота 290 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1217,7 +1217,7 @@
 Ширина 200 см, высота 295 см. Ширина рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1264,7 +1264,7 @@
 Ширина 300 см, высота 220 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1311,7 +1311,7 @@
 Ширина 300 см, высота 225 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1358,7 +1358,7 @@
 Ширина 300 см, высота 230 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1405,7 +1405,7 @@
 Ширина 300 см, высота 235 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1452,7 +1452,7 @@
 Ширина 300 см, высота 240 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1499,7 +1499,7 @@
 Ширина 300 см, высота 245 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1546,7 +1546,7 @@
 Ширина 300 см, высота 250 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1593,7 +1593,7 @@
 Ширина 300 см, высота 255 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1640,7 +1640,7 @@
 Ширина 300 см, высота 260 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1687,7 +1687,7 @@
 Ширина 300 см, высота 265 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1734,7 +1734,7 @@
 Ширина 300 см, высота 270 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1781,7 +1781,7 @@
 Ширина 300 см, высота 275 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1828,7 +1828,7 @@
 Ширина 300 см, высота 280 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1875,7 +1875,7 @@
 Ширина 300 см, высота 285 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1922,7 +1922,7 @@
 Ширина 300 см, высота 290 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -1969,7 +1969,7 @@
 Ширина 300 см, высота 295 см. Ширина рассчитана на стандартное окно 1,3–1,5 м с классической сборкой: полотно ложится мягкой равномерной волной. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2016,7 +2016,7 @@
 Ширина 400 см, высота 220 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2063,7 +2063,7 @@
 Ширина 400 см, высота 225 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2110,7 +2110,7 @@
 Ширина 400 см, высота 230 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2157,7 +2157,7 @@
 Ширина 400 см, высота 235 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2204,7 +2204,7 @@
 Ширина 400 см, высота 240 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2251,7 +2251,7 @@
 Ширина 400 см, высота 245 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2298,7 +2298,7 @@
 Ширина 400 см, высота 250 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2345,7 +2345,7 @@
 Ширина 400 см, высота 255 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2392,7 +2392,7 @@
 Ширина 400 см, высота 260 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2439,7 +2439,7 @@
 Ширина 400 см, высота 265 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2486,7 +2486,7 @@
 Ширина 400 см, высота 270 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2533,7 +2533,7 @@
 Ширина 400 см, высота 275 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2580,7 +2580,7 @@
 Ширина 400 см, высота 280 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2627,7 +2627,7 @@
 Ширина 400 см, высота 285 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2674,7 +2674,7 @@
 Ширина 400 см, высота 290 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2721,7 +2721,7 @@
 Ширина 400 см, высота 295 см. Ширина рассчитана на окно с балконной дверью или проём шириной 1,8–2 м: полотно ложится красивой плотной сборкой по всей ширине. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2768,7 +2768,7 @@
 Ширина 500 см, высота 220 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2815,7 +2815,7 @@
 Ширина 500 см, высота 225 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2862,7 +2862,7 @@
 Ширина 500 см, высота 230 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2909,7 +2909,7 @@
 Ширина 500 см, высота 235 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -2956,7 +2956,7 @@
 Ширина 500 см, высота 240 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3003,7 +3003,7 @@
 Ширина 500 см, высота 245 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3050,7 +3050,7 @@
 Ширина 500 см, высота 250 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3097,7 +3097,7 @@
 Ширина 500 см, высота 255 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3144,7 +3144,7 @@
 Ширина 500 см, высота 260 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3191,7 +3191,7 @@
 Ширина 500 см, высота 265 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3238,7 +3238,7 @@
 Ширина 500 см, высота 270 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3285,7 +3285,7 @@
 Ширина 500 см, высота 275 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3332,7 +3332,7 @@
 Ширина 500 см, высота 280 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3379,7 +3379,7 @@
 Ширина 500 см, высота 285 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3426,7 +3426,7 @@
 Ширина 500 см, высота 290 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3473,7 +3473,7 @@
 Ширина 500 см, высота 295 см. Ширина рассчитана на широкое окно 2,2–2,5 м с богатой драпировкой: полотно ложится глубокой пышной волной. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3520,7 +3520,7 @@
 Ширина 600 см, высота 220 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3567,7 +3567,7 @@
 Ширина 600 см, высота 225 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3614,7 +3614,7 @@
 Ширина 600 см, высота 230 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3661,7 +3661,7 @@
 Ширина 600 см, высота 235 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3708,7 +3708,7 @@
 Ширина 600 см, высота 240 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3755,7 +3755,7 @@
 Ширина 600 см, высота 245 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3802,7 +3802,7 @@
 Ширина 600 см, высота 250 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3849,7 +3849,7 @@
 Ширина 600 см, высота 255 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3896,7 +3896,7 @@
 Ширина 600 см, высота 260 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3943,7 +3943,7 @@
 Ширина 600 см, высота 265 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -3990,7 +3990,7 @@
 Ширина 600 см, высота 270 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4037,7 +4037,7 @@
 Ширина 600 см, высота 275 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4084,7 +4084,7 @@
 Ширина 600 см, высота 280 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4131,7 +4131,7 @@
 Ширина 600 см, высота 285 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4178,7 +4178,7 @@
 Ширина 600 см, высота 290 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4225,7 +4225,7 @@
 Ширина 600 см, высота 295 см. Ширина рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4272,7 +4272,7 @@
 Ширина 700 см, высота 220 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4319,7 +4319,7 @@
 Ширина 700 см, высота 225 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4366,7 +4366,7 @@
 Ширина 700 см, высота 230 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4413,7 +4413,7 @@
 Ширина 700 см, высота 235 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4460,7 +4460,7 @@
 Ширина 700 см, высота 240 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4507,7 +4507,7 @@
 Ширина 700 см, высота 245 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4554,7 +4554,7 @@
 Ширина 700 см, высота 250 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4601,7 +4601,7 @@
 Ширина 700 см, высота 255 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4648,7 +4648,7 @@
 Ширина 700 см, высота 260 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4695,7 +4695,7 @@
 Ширина 700 см, высота 265 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4742,7 +4742,7 @@
 Ширина 700 см, высота 270 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4789,7 +4789,7 @@
 Ширина 700 см, высота 275 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4836,7 +4836,7 @@
 Ширина 700 см, высота 280 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4883,7 +4883,7 @@
 Ширина 700 см, высота 285 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4930,7 +4930,7 @@
 Ширина 700 см, высота 290 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -4977,7 +4977,7 @@
 Ширина 700 см, высота 295 см. Ширина рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5024,7 +5024,7 @@
 Ширина 800 см, высота 220 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 220 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5071,7 +5071,7 @@
 Ширина 800 см, высота 225 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 225 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5118,7 +5118,7 @@
 Ширина 800 см, высота 230 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 230 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5165,7 +5165,7 @@
 Ширина 800 см, высота 235 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 235 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5212,7 +5212,7 @@
 Ширина 800 см, высота 240 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 240 см подобрана для стандартных потолков 2,5–2,7 м — тюль висит чуть выше подоконника или до пола в типовой квартире. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5259,7 +5259,7 @@
 Ширина 800 см, высота 245 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 245 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5306,7 +5306,7 @@
 Ширина 800 см, высота 250 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 250 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5353,7 +5353,7 @@
 Ширина 800 см, высота 255 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 255 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5400,7 +5400,7 @@
 Ширина 800 см, высота 260 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 260 см подобрана для потолков 2,7–2,9 м — тюль висит в пол с небольшим запасом на подгиб. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5447,7 +5447,7 @@
 Ширина 800 см, высота 265 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 265 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5494,7 +5494,7 @@
 Ширина 800 см, высота 270 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 270 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5541,7 +5541,7 @@
 Ширина 800 см, высота 275 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 275 см подобрана для высоких потолков 2,9–3,0 м — тюль висит в пол в новостройке или доме с высокими потолками. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5588,7 +5588,7 @@
 Ширина 800 см, высота 280 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 280 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5635,7 +5635,7 @@
 Ширина 800 см, высота 285 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 285 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5682,7 +5682,7 @@
 Ширина 800 см, высота 290 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 290 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5729,7 +5729,7 @@
 Ширина 800 см, высота 295 см. Ширина рассчитана на панорамное остекление, эркер или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов. Высота 295 см подобрана для очень высоких потолков от 3,0 м — тюль висит в пол под самый потолок в доме, студии или лофте. Перед заказом измерьте длину карниза и расстояние от него до пола.
 ЧТО ЭТО ЗА ТКАНЬ
 Вуаль — тонкая однотонная ткань без рисунка, матовая, без блеска и «стеклянного» эффекта. Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными. Ткань пропускает дневной свет, но скрывает комнату от взглядов с улицы, не электризуется и не притягивает пыль.
-ГОТОВ К ПОВЕШЕНИЮ
+ГОТОВА К ВЫВЕШИВАНИЮ
 Верх обработан шторной лентой (тесьмой) шириной 4 см с двумя хлопковыми нитями — сборка регулируется вручную под нужную пышность. Лента подходит для карнизов с крючками, для круглых и профильных карнизов. Боковые швы обработаны ролевым швом: тонкий аккуратный край без утолщений и торчащих ниток, низ ровный и подшитый.
 УХОД
 Стирка при 30 °C в режиме деликатной стирки, отжим минимальный или без отжима. Гладить тёплым утюгом через ткань либо повесить влажным — вуаль расправляется сама под собственным весом.
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Название, блок «Готов к повешению»</t>
+          <t>Название, блок «Готова к вывешиванию»</t>
         </is>
       </c>
     </row>
